--- a/data/processed_data/Dataset_Malaria.xlsx
+++ b/data/processed_data/Dataset_Malaria.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N1873"/>
+  <dimension ref="A1:N1872"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -96635,7 +96635,7 @@
       </c>
       <c r="C1789" t="inlineStr">
         <is>
-          <t>BELLA VISTA</t>
+          <t>SAN JOSE OLERO</t>
         </is>
       </c>
       <c r="D1789">
@@ -96643,7 +96643,7 @@
       </c>
       <c r="E1789" t="inlineStr">
         <is>
-          <t>2023-07-20</t>
+          <t>2023-07-18</t>
         </is>
       </c>
       <c r="F1789" t="inlineStr">
@@ -96653,7 +96653,7 @@
       </c>
       <c r="G1789" t="inlineStr">
         <is>
-          <t>OCHLEROTATUS SCAPULARIS</t>
+          <t>ANOPHELES GALVAOI</t>
         </is>
       </c>
       <c r="H1789">
@@ -96666,12 +96666,12 @@
       </c>
       <c r="L1789" t="inlineStr">
         <is>
-          <t>-22.1189868181117</t>
+          <t>-22.1413481104474</t>
         </is>
       </c>
       <c r="M1789" t="inlineStr">
         <is>
-          <t>-56.520911263753</t>
+          <t>-56.5214756804953</t>
         </is>
       </c>
     </row>
@@ -96741,7 +96741,7 @@
       </c>
       <c r="C1791" t="inlineStr">
         <is>
-          <t>SAN JOSE OLERO</t>
+          <t>APAMI</t>
         </is>
       </c>
       <c r="D1791">
@@ -96749,7 +96749,7 @@
       </c>
       <c r="E1791" t="inlineStr">
         <is>
-          <t>2023-07-18</t>
+          <t>2023-07-19</t>
         </is>
       </c>
       <c r="F1791" t="inlineStr">
@@ -96812,7 +96812,7 @@
       </c>
       <c r="G1792" t="inlineStr">
         <is>
-          <t>ANOPHELES GALVAOI</t>
+          <t>ANOPHELES OSWALDOI</t>
         </is>
       </c>
       <c r="H1792">
@@ -96865,7 +96865,7 @@
       </c>
       <c r="G1793" t="inlineStr">
         <is>
-          <t>ANOPHELES OSWALDOI</t>
+          <t>ANOPHELES GALVAOI</t>
         </is>
       </c>
       <c r="H1793">
@@ -96918,7 +96918,7 @@
       </c>
       <c r="G1794" t="inlineStr">
         <is>
-          <t>ANOPHELES GALVAOI</t>
+          <t>ANOPHELES OSWALDOI</t>
         </is>
       </c>
       <c r="H1794">
@@ -96961,7 +96961,7 @@
       </c>
       <c r="E1795" t="inlineStr">
         <is>
-          <t>2023-07-19</t>
+          <t>2023-07-20</t>
         </is>
       </c>
       <c r="F1795" t="inlineStr">
@@ -96971,7 +96971,7 @@
       </c>
       <c r="G1795" t="inlineStr">
         <is>
-          <t>ANOPHELES OSWALDOI</t>
+          <t>ANOPHELES EVANSAE</t>
         </is>
       </c>
       <c r="H1795">
@@ -96984,29 +96984,29 @@
       </c>
       <c r="L1795" t="inlineStr">
         <is>
-          <t>-22.1413481104474</t>
+          <t>-22.1419075846657</t>
         </is>
       </c>
       <c r="M1795" t="inlineStr">
         <is>
-          <t>-56.5214756804953</t>
+          <t>-56.5181863721249</t>
         </is>
       </c>
     </row>
     <row r="1796">
       <c r="A1796" t="inlineStr">
         <is>
-          <t>AMAMBAY</t>
+          <t>NEEMBUCU</t>
         </is>
       </c>
       <c r="B1796" t="inlineStr">
         <is>
-          <t>BELLA VISTA</t>
+          <t>CERRITO</t>
         </is>
       </c>
       <c r="C1796" t="inlineStr">
         <is>
-          <t>APAMI</t>
+          <t>CERRITO</t>
         </is>
       </c>
       <c r="D1796">
@@ -97014,7 +97014,7 @@
       </c>
       <c r="E1796" t="inlineStr">
         <is>
-          <t>2023-07-20</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="F1796" t="inlineStr">
@@ -97024,7 +97024,7 @@
       </c>
       <c r="G1796" t="inlineStr">
         <is>
-          <t>ANOPHELES EVANSAE</t>
+          <t>ANOPHELES ALBITARSIS</t>
         </is>
       </c>
       <c r="H1796">
@@ -97037,12 +97037,12 @@
       </c>
       <c r="L1796" t="inlineStr">
         <is>
-          <t>-22.1419075846657</t>
+          <t>-27.344827</t>
         </is>
       </c>
       <c r="M1796" t="inlineStr">
         <is>
-          <t>-56.5181863721249</t>
+          <t>-57.650836</t>
         </is>
       </c>
     </row>
@@ -97077,7 +97077,7 @@
       </c>
       <c r="G1797" t="inlineStr">
         <is>
-          <t>ANOPHELES ALBITARSIS</t>
+          <t>ANPHELES (COMPLEJO) ALBITARSIS</t>
         </is>
       </c>
       <c r="H1797">
@@ -97130,7 +97130,7 @@
       </c>
       <c r="G1798" t="inlineStr">
         <is>
-          <t>ANPHELES (COMPLEJO) ALBITARSIS</t>
+          <t>ANOPHELES ALBITARSIS</t>
         </is>
       </c>
       <c r="H1798">
@@ -97173,7 +97173,7 @@
       </c>
       <c r="E1799" t="inlineStr">
         <is>
-          <t>2023-08-28</t>
+          <t>2023-08-29</t>
         </is>
       </c>
       <c r="F1799" t="inlineStr">
@@ -97196,12 +97196,12 @@
       </c>
       <c r="L1799" t="inlineStr">
         <is>
-          <t>-27.344827</t>
+          <t>-27.344343</t>
         </is>
       </c>
       <c r="M1799" t="inlineStr">
         <is>
-          <t>-57.650836</t>
+          <t>-57.64769</t>
         </is>
       </c>
     </row>
@@ -97236,7 +97236,7 @@
       </c>
       <c r="G1800" t="inlineStr">
         <is>
-          <t>ANOPHELES ALBITARSIS</t>
+          <t>ANOPHELES (COMPLEJO) ALBITARSIS</t>
         </is>
       </c>
       <c r="H1800">
@@ -97289,7 +97289,7 @@
       </c>
       <c r="G1801" t="inlineStr">
         <is>
-          <t>ANOPHELES (COMPLEJO) ALBITARSIS</t>
+          <t>ANOPHELES ALBITARSIS</t>
         </is>
       </c>
       <c r="H1801">
@@ -97342,7 +97342,7 @@
       </c>
       <c r="G1802" t="inlineStr">
         <is>
-          <t>ANOPHELES ALBITARSIS</t>
+          <t>ANOPHELES TRIANNULATUS</t>
         </is>
       </c>
       <c r="H1802">
@@ -97395,7 +97395,7 @@
       </c>
       <c r="G1803" t="inlineStr">
         <is>
-          <t>ANOPHELES TRIANNULATUS</t>
+          <t>ANOPHELES GALVAOI</t>
         </is>
       </c>
       <c r="H1803">
@@ -97438,7 +97438,7 @@
       </c>
       <c r="E1804" t="inlineStr">
         <is>
-          <t>2023-08-29</t>
+          <t>2023-08-30</t>
         </is>
       </c>
       <c r="F1804" t="inlineStr">
@@ -97448,7 +97448,7 @@
       </c>
       <c r="G1804" t="inlineStr">
         <is>
-          <t>ANOPHELES GALVAOI</t>
+          <t>ANOPHELES ALBITARSIS</t>
         </is>
       </c>
       <c r="H1804">
@@ -97461,12 +97461,12 @@
       </c>
       <c r="L1804" t="inlineStr">
         <is>
-          <t>-27.344343</t>
+          <t>-27.343431</t>
         </is>
       </c>
       <c r="M1804" t="inlineStr">
         <is>
-          <t>-57.64769</t>
+          <t>-57.636472</t>
         </is>
       </c>
     </row>
@@ -97501,7 +97501,7 @@
       </c>
       <c r="G1805" t="inlineStr">
         <is>
-          <t>ANOPHELES ALBITARSIS</t>
+          <t>ANOPHELES (COMPLEJO) ALBITARSIS</t>
         </is>
       </c>
       <c r="H1805">
@@ -97554,7 +97554,7 @@
       </c>
       <c r="G1806" t="inlineStr">
         <is>
-          <t>ANOPHELES (COMPLEJO) ALBITARSIS</t>
+          <t>ANOPHELES TRIANNULATUS</t>
         </is>
       </c>
       <c r="H1806">
@@ -97607,7 +97607,7 @@
       </c>
       <c r="G1807" t="inlineStr">
         <is>
-          <t>ANOPHELES TRIANNULATUS</t>
+          <t>ANOPHELES ALBITARSIS</t>
         </is>
       </c>
       <c r="H1807">
@@ -97660,7 +97660,7 @@
       </c>
       <c r="G1808" t="inlineStr">
         <is>
-          <t>ANOPHELES ALBITARSIS</t>
+          <t>ANOPHELES GALVAOI</t>
         </is>
       </c>
       <c r="H1808">
@@ -97703,7 +97703,7 @@
       </c>
       <c r="E1809" t="inlineStr">
         <is>
-          <t>2023-08-30</t>
+          <t>2023-08-31</t>
         </is>
       </c>
       <c r="F1809" t="inlineStr">
@@ -97713,7 +97713,7 @@
       </c>
       <c r="G1809" t="inlineStr">
         <is>
-          <t>ANOPHELES GALVAOI</t>
+          <t>ANOPHELES ALBITARSIS</t>
         </is>
       </c>
       <c r="H1809">
@@ -97726,12 +97726,12 @@
       </c>
       <c r="L1809" t="inlineStr">
         <is>
-          <t>-27.343431</t>
+          <t>-27.344343</t>
         </is>
       </c>
       <c r="M1809" t="inlineStr">
         <is>
-          <t>-57.636472</t>
+          <t>-57.647692</t>
         </is>
       </c>
     </row>
@@ -97809,7 +97809,7 @@
       </c>
       <c r="E1811" t="inlineStr">
         <is>
-          <t>2023-08-31</t>
+          <t>2023-08-29</t>
         </is>
       </c>
       <c r="F1811" t="inlineStr">
@@ -97832,29 +97832,29 @@
       </c>
       <c r="L1811" t="inlineStr">
         <is>
-          <t>-27.344343</t>
+          <t>-27.343179</t>
         </is>
       </c>
       <c r="M1811" t="inlineStr">
         <is>
-          <t>-57.647692</t>
+          <t>-57.645754</t>
         </is>
       </c>
     </row>
     <row r="1812">
       <c r="A1812" t="inlineStr">
         <is>
-          <t>NEEMBUCU</t>
+          <t>SAN PEDRO</t>
         </is>
       </c>
       <c r="B1812" t="inlineStr">
         <is>
-          <t>CERRITO</t>
+          <t>ANTEQUERA</t>
         </is>
       </c>
       <c r="C1812" t="inlineStr">
         <is>
-          <t>CERRITO</t>
+          <t>ANTEQUERA</t>
         </is>
       </c>
       <c r="D1812">
@@ -97862,7 +97862,7 @@
       </c>
       <c r="E1812" t="inlineStr">
         <is>
-          <t>2023-08-29</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="F1812" t="inlineStr">
@@ -97885,12 +97885,12 @@
       </c>
       <c r="L1812" t="inlineStr">
         <is>
-          <t>-27.343179</t>
+          <t>-24.087057</t>
         </is>
       </c>
       <c r="M1812" t="inlineStr">
         <is>
-          <t>-57.645754</t>
+          <t>-57.19029</t>
         </is>
       </c>
     </row>
@@ -97915,7 +97915,7 @@
       </c>
       <c r="E1813" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2023-09-13</t>
         </is>
       </c>
       <c r="F1813" t="inlineStr">
@@ -98031,7 +98031,7 @@
       </c>
       <c r="G1815" t="inlineStr">
         <is>
-          <t>ANOPHELES ALBITARSIS</t>
+          <t>ANOPHELES TRIANNULATUS</t>
         </is>
       </c>
       <c r="H1815">
@@ -98084,7 +98084,7 @@
       </c>
       <c r="G1816" t="inlineStr">
         <is>
-          <t>ANOPHELES TRIANNULATUS</t>
+          <t>ANOPHELES RONDONI</t>
         </is>
       </c>
       <c r="H1816">
@@ -98127,7 +98127,7 @@
       </c>
       <c r="E1817" t="inlineStr">
         <is>
-          <t>2023-09-13</t>
+          <t>2023-09-14</t>
         </is>
       </c>
       <c r="F1817" t="inlineStr">
@@ -98137,7 +98137,7 @@
       </c>
       <c r="G1817" t="inlineStr">
         <is>
-          <t>ANOPHELES RONDONI</t>
+          <t>ANOPHELES ALBITARSIS</t>
         </is>
       </c>
       <c r="H1817">
@@ -98150,12 +98150,12 @@
       </c>
       <c r="L1817" t="inlineStr">
         <is>
-          <t>-24.087057</t>
+          <t>-24.071613</t>
         </is>
       </c>
       <c r="M1817" t="inlineStr">
         <is>
-          <t>-57.19029</t>
+          <t>-57.208397</t>
         </is>
       </c>
     </row>
@@ -98190,7 +98190,7 @@
       </c>
       <c r="G1818" t="inlineStr">
         <is>
-          <t>ANOPHELES ALBITARSIS</t>
+          <t>ANOPHELES TRIANNULATUS</t>
         </is>
       </c>
       <c r="H1818">
@@ -98243,7 +98243,7 @@
       </c>
       <c r="G1819" t="inlineStr">
         <is>
-          <t>ANOPHELES TRIANNULATUS</t>
+          <t>ANOPHELES ALBITARSIS</t>
         </is>
       </c>
       <c r="H1819">
@@ -98296,7 +98296,7 @@
       </c>
       <c r="G1820" t="inlineStr">
         <is>
-          <t>ANOPHELES ALBITARSIS</t>
+          <t>ANOPHELES STRODEI</t>
         </is>
       </c>
       <c r="H1820">
@@ -98349,7 +98349,7 @@
       </c>
       <c r="G1821" t="inlineStr">
         <is>
-          <t>ANOPHELES STRODEI</t>
+          <t>ANOPHELES TRIANNULATUS</t>
         </is>
       </c>
       <c r="H1821">
@@ -98392,7 +98392,7 @@
       </c>
       <c r="E1822" t="inlineStr">
         <is>
-          <t>2023-09-14</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="F1822" t="inlineStr">
@@ -98402,7 +98402,7 @@
       </c>
       <c r="G1822" t="inlineStr">
         <is>
-          <t>ANOPHELES TRIANNULATUS</t>
+          <t>ANOPHELES ALBITARSIS</t>
         </is>
       </c>
       <c r="H1822">
@@ -98415,12 +98415,12 @@
       </c>
       <c r="L1822" t="inlineStr">
         <is>
-          <t>-24.071613</t>
+          <t>-24.087057</t>
         </is>
       </c>
       <c r="M1822" t="inlineStr">
         <is>
-          <t>-57.208397</t>
+          <t>-57.19029</t>
         </is>
       </c>
     </row>
@@ -98455,7 +98455,7 @@
       </c>
       <c r="G1823" t="inlineStr">
         <is>
-          <t>ANOPHELES ALBITARSIS</t>
+          <t>ANOPHELES TRIANNULATUS</t>
         </is>
       </c>
       <c r="H1823">
@@ -98508,7 +98508,7 @@
       </c>
       <c r="G1824" t="inlineStr">
         <is>
-          <t>ANOPHELES TRIANNULATUS</t>
+          <t>ANOPHELES SSP</t>
         </is>
       </c>
       <c r="H1824">
@@ -98533,17 +98533,17 @@
     <row r="1825">
       <c r="A1825" t="inlineStr">
         <is>
-          <t>SAN PEDRO</t>
+          <t>BOQUERON</t>
         </is>
       </c>
       <c r="B1825" t="inlineStr">
         <is>
-          <t>ANTEQUERA</t>
+          <t>MARISCAL ESTIGARRIBIA</t>
         </is>
       </c>
       <c r="C1825" t="inlineStr">
         <is>
-          <t>ANTEQUERA</t>
+          <t>INFANTE RIVAROLA</t>
         </is>
       </c>
       <c r="D1825">
@@ -98551,7 +98551,7 @@
       </c>
       <c r="E1825" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2023-09-19</t>
         </is>
       </c>
       <c r="F1825" t="inlineStr">
@@ -98561,7 +98561,7 @@
       </c>
       <c r="G1825" t="inlineStr">
         <is>
-          <t>ANOPHELES SSP</t>
+          <t>ANOPHELES ALBITARSIS</t>
         </is>
       </c>
       <c r="H1825">
@@ -98574,12 +98574,12 @@
       </c>
       <c r="L1825" t="inlineStr">
         <is>
-          <t>-24.087057</t>
+          <t>-21.679521</t>
         </is>
       </c>
       <c r="M1825" t="inlineStr">
         <is>
-          <t>-57.19029</t>
+          <t>-62.401436</t>
         </is>
       </c>
     </row>
@@ -98604,7 +98604,7 @@
       </c>
       <c r="E1826" t="inlineStr">
         <is>
-          <t>2023-09-19</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="F1826" t="inlineStr">
@@ -98627,29 +98627,29 @@
       </c>
       <c r="L1826" t="inlineStr">
         <is>
-          <t>-21.679521</t>
+          <t>-21.671929</t>
         </is>
       </c>
       <c r="M1826" t="inlineStr">
         <is>
-          <t>-62.401436</t>
+          <t>-62.456246</t>
         </is>
       </c>
     </row>
     <row r="1827">
       <c r="A1827" t="inlineStr">
         <is>
-          <t>BOQUERON</t>
+          <t>CONCEPCION</t>
         </is>
       </c>
       <c r="B1827" t="inlineStr">
         <is>
-          <t>MARISCAL ESTIGARRIBIA</t>
+          <t>CONCEPCION</t>
         </is>
       </c>
       <c r="C1827" t="inlineStr">
         <is>
-          <t>INFANTE RIVAROLA</t>
+          <t>SAN ANTONIO</t>
         </is>
       </c>
       <c r="D1827">
@@ -98657,7 +98657,7 @@
       </c>
       <c r="E1827" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
+          <t>2023-10-16</t>
         </is>
       </c>
       <c r="F1827" t="inlineStr">
@@ -98680,12 +98680,12 @@
       </c>
       <c r="L1827" t="inlineStr">
         <is>
-          <t>-21.671929</t>
+          <t>-23.419459</t>
         </is>
       </c>
       <c r="M1827" t="inlineStr">
         <is>
-          <t>-62.456246</t>
+          <t>-57.449392</t>
         </is>
       </c>
     </row>
@@ -98710,7 +98710,7 @@
       </c>
       <c r="E1828" t="inlineStr">
         <is>
-          <t>2023-10-16</t>
+          <t>2023-10-17</t>
         </is>
       </c>
       <c r="F1828" t="inlineStr">
@@ -98733,12 +98733,12 @@
       </c>
       <c r="L1828" t="inlineStr">
         <is>
-          <t>-23.419459</t>
+          <t>-23.390867</t>
         </is>
       </c>
       <c r="M1828" t="inlineStr">
         <is>
-          <t>-57.449392</t>
+          <t>-57.45968</t>
         </is>
       </c>
     </row>
@@ -98816,7 +98816,7 @@
       </c>
       <c r="E1830" t="inlineStr">
         <is>
-          <t>2023-10-17</t>
+          <t>2023-10-18</t>
         </is>
       </c>
       <c r="F1830" t="inlineStr">
@@ -98839,29 +98839,29 @@
       </c>
       <c r="L1830" t="inlineStr">
         <is>
-          <t>-23.390867</t>
+          <t>-23.419459</t>
         </is>
       </c>
       <c r="M1830" t="inlineStr">
         <is>
-          <t>-57.45968</t>
+          <t>-57.449392</t>
         </is>
       </c>
     </row>
     <row r="1831">
       <c r="A1831" t="inlineStr">
         <is>
-          <t>CONCEPCION</t>
+          <t>ALTO PARAGUAY</t>
         </is>
       </c>
       <c r="B1831" t="inlineStr">
         <is>
-          <t>CONCEPCION</t>
+          <t>CARMELO PERALTA</t>
         </is>
       </c>
       <c r="C1831" t="inlineStr">
         <is>
-          <t>SAN ANTONIO</t>
+          <t>CARMELO PERALTA</t>
         </is>
       </c>
       <c r="D1831">
@@ -98869,7 +98869,7 @@
       </c>
       <c r="E1831" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
+          <t>2023-10-26</t>
         </is>
       </c>
       <c r="F1831" t="inlineStr">
@@ -98892,12 +98892,12 @@
       </c>
       <c r="L1831" t="inlineStr">
         <is>
-          <t>-23.419459</t>
+          <t>-21.690887</t>
         </is>
       </c>
       <c r="M1831" t="inlineStr">
         <is>
-          <t>-57.449392</t>
+          <t>-57.897595</t>
         </is>
       </c>
     </row>
@@ -98922,7 +98922,7 @@
       </c>
       <c r="E1832" t="inlineStr">
         <is>
-          <t>2023-10-26</t>
+          <t>2023-10-25</t>
         </is>
       </c>
       <c r="F1832" t="inlineStr">
@@ -98945,12 +98945,12 @@
       </c>
       <c r="L1832" t="inlineStr">
         <is>
-          <t>-21.690887</t>
+          <t>-21.690619</t>
         </is>
       </c>
       <c r="M1832" t="inlineStr">
         <is>
-          <t>-57.897595</t>
+          <t>-57.89738</t>
         </is>
       </c>
     </row>
@@ -98975,7 +98975,7 @@
       </c>
       <c r="E1833" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
+          <t>2023-10-24</t>
         </is>
       </c>
       <c r="F1833" t="inlineStr">
@@ -98985,7 +98985,7 @@
       </c>
       <c r="G1833" t="inlineStr">
         <is>
-          <t>ANOPHELES ALBITARSIS</t>
+          <t>ANOPHELES SSP</t>
         </is>
       </c>
       <c r="H1833">
@@ -98998,12 +98998,12 @@
       </c>
       <c r="L1833" t="inlineStr">
         <is>
-          <t>-21.690619</t>
+          <t>-25.035293</t>
         </is>
       </c>
       <c r="M1833" t="inlineStr">
         <is>
-          <t>-57.89738</t>
+          <t>-57.868627</t>
         </is>
       </c>
     </row>
@@ -99038,7 +99038,7 @@
       </c>
       <c r="G1834" t="inlineStr">
         <is>
-          <t>ANOPHELES SSP</t>
+          <t>ANOPHELES ALBITARSIS</t>
         </is>
       </c>
       <c r="H1834">
@@ -99091,7 +99091,7 @@
       </c>
       <c r="G1835" t="inlineStr">
         <is>
-          <t>ANOPHELES ALBITARSIS</t>
+          <t>ANOPHELES RONDONI</t>
         </is>
       </c>
       <c r="H1835">
@@ -99144,7 +99144,7 @@
       </c>
       <c r="G1836" t="inlineStr">
         <is>
-          <t>ANOPHELES RONDONI</t>
+          <t>ANOPHELES ALBITARSIS</t>
         </is>
       </c>
       <c r="H1836">
@@ -99169,17 +99169,17 @@
     <row r="1837">
       <c r="A1837" t="inlineStr">
         <is>
-          <t>ALTO PARAGUAY</t>
+          <t>AMAMBAY</t>
         </is>
       </c>
       <c r="B1837" t="inlineStr">
         <is>
-          <t>CARMELO PERALTA</t>
+          <t>BELLA VISTA</t>
         </is>
       </c>
       <c r="C1837" t="inlineStr">
         <is>
-          <t>CARMELO PERALTA</t>
+          <t>BELLA VISTA</t>
         </is>
       </c>
       <c r="D1837">
@@ -99187,7 +99187,7 @@
       </c>
       <c r="E1837" t="inlineStr">
         <is>
-          <t>2023-10-24</t>
+          <t>2023-11-16</t>
         </is>
       </c>
       <c r="F1837" t="inlineStr">
@@ -99197,7 +99197,7 @@
       </c>
       <c r="G1837" t="inlineStr">
         <is>
-          <t>ANOPHELES ALBITARSIS</t>
+          <t>ANOPHELES GALVAOI</t>
         </is>
       </c>
       <c r="H1837">
@@ -99210,12 +99210,12 @@
       </c>
       <c r="L1837" t="inlineStr">
         <is>
-          <t>-25.035293</t>
+          <t>-22.1189868181117</t>
         </is>
       </c>
       <c r="M1837" t="inlineStr">
         <is>
-          <t>-57.868627</t>
+          <t>-56.520911263753</t>
         </is>
       </c>
     </row>
@@ -99240,7 +99240,7 @@
       </c>
       <c r="E1838" t="inlineStr">
         <is>
-          <t>2023-11-16</t>
+          <t>2023-11-15</t>
         </is>
       </c>
       <c r="F1838" t="inlineStr">
@@ -99263,12 +99263,12 @@
       </c>
       <c r="L1838" t="inlineStr">
         <is>
-          <t>-22.1189868181117</t>
+          <t>-22.1413481104474</t>
         </is>
       </c>
       <c r="M1838" t="inlineStr">
         <is>
-          <t>-56.520911263753</t>
+          <t>-56.5214756804953</t>
         </is>
       </c>
     </row>
@@ -99303,7 +99303,7 @@
       </c>
       <c r="G1839" t="inlineStr">
         <is>
-          <t>ANOPHELES GALVAOI</t>
+          <t>ANOPHELES EVANSAE</t>
         </is>
       </c>
       <c r="H1839">
@@ -99356,7 +99356,7 @@
       </c>
       <c r="G1840" t="inlineStr">
         <is>
-          <t>ANOPHELES EVANSAE</t>
+          <t>ANOPHELES PARVUS</t>
         </is>
       </c>
       <c r="H1840">
@@ -99409,7 +99409,7 @@
       </c>
       <c r="G1841" t="inlineStr">
         <is>
-          <t>ANOPHELES PARVUS</t>
+          <t>ANOPHELES ANTUNESI</t>
         </is>
       </c>
       <c r="H1841">
@@ -99452,7 +99452,7 @@
       </c>
       <c r="E1842" t="inlineStr">
         <is>
-          <t>2023-11-15</t>
+          <t>2023-11-14</t>
         </is>
       </c>
       <c r="F1842" t="inlineStr">
@@ -99462,7 +99462,7 @@
       </c>
       <c r="G1842" t="inlineStr">
         <is>
-          <t>ANOPHELES ANTUNESI</t>
+          <t>ANOPHELES GALVAOI</t>
         </is>
       </c>
       <c r="H1842">
@@ -99515,7 +99515,7 @@
       </c>
       <c r="G1843" t="inlineStr">
         <is>
-          <t>ANOPHELES GALVAOI</t>
+          <t>ANOPHELES OSWALDOI</t>
         </is>
       </c>
       <c r="H1843">
@@ -99568,7 +99568,7 @@
       </c>
       <c r="G1844" t="inlineStr">
         <is>
-          <t>ANOPHELES OSWALDOI</t>
+          <t>ANOPHELES EVANSAE</t>
         </is>
       </c>
       <c r="H1844">
@@ -99621,7 +99621,7 @@
       </c>
       <c r="G1845" t="inlineStr">
         <is>
-          <t>ANOPHELES EVANSAE</t>
+          <t>ANOPHELES PARVUS</t>
         </is>
       </c>
       <c r="H1845">
@@ -99674,7 +99674,7 @@
       </c>
       <c r="G1846" t="inlineStr">
         <is>
-          <t>ANOPHELES PARVUS</t>
+          <t>ANOPHELES ANTUNESI</t>
         </is>
       </c>
       <c r="H1846">
@@ -99717,7 +99717,7 @@
       </c>
       <c r="E1847" t="inlineStr">
         <is>
-          <t>2023-11-14</t>
+          <t>2023-11-16</t>
         </is>
       </c>
       <c r="F1847" t="inlineStr">
@@ -99740,29 +99740,29 @@
       </c>
       <c r="L1847" t="inlineStr">
         <is>
-          <t>-22.1413481104474</t>
+          <t>-22.1414132557562</t>
         </is>
       </c>
       <c r="M1847" t="inlineStr">
         <is>
-          <t>-56.5214756804953</t>
+          <t>-56.5190511192164</t>
         </is>
       </c>
     </row>
     <row r="1848">
       <c r="A1848" t="inlineStr">
         <is>
-          <t>AMAMBAY</t>
+          <t>NEEMBUCU</t>
         </is>
       </c>
       <c r="B1848" t="inlineStr">
         <is>
-          <t>BELLA VISTA</t>
+          <t>CERRITO</t>
         </is>
       </c>
       <c r="C1848" t="inlineStr">
         <is>
-          <t>BELLA VISTA</t>
+          <t>CERRITO</t>
         </is>
       </c>
       <c r="D1848">
@@ -99770,7 +99770,7 @@
       </c>
       <c r="E1848" t="inlineStr">
         <is>
-          <t>2023-11-16</t>
+          <t>2023-11-28</t>
         </is>
       </c>
       <c r="F1848" t="inlineStr">
@@ -99780,7 +99780,7 @@
       </c>
       <c r="G1848" t="inlineStr">
         <is>
-          <t>ANOPHELES ANTUNESI</t>
+          <t>ANOPHELES ALBITARSIS</t>
         </is>
       </c>
       <c r="H1848">
@@ -99793,12 +99793,12 @@
       </c>
       <c r="L1848" t="inlineStr">
         <is>
-          <t>-22.1414132557562</t>
+          <t>-25.343179</t>
         </is>
       </c>
       <c r="M1848" t="inlineStr">
         <is>
-          <t>-56.5190511192164</t>
+          <t>-57.645754</t>
         </is>
       </c>
     </row>
@@ -99939,7 +99939,7 @@
       </c>
       <c r="G1851" t="inlineStr">
         <is>
-          <t>ANOPHELES ALBITARSIS</t>
+          <t>ANOPHELES GALVAOI</t>
         </is>
       </c>
       <c r="H1851">
@@ -99982,7 +99982,7 @@
       </c>
       <c r="E1852" t="inlineStr">
         <is>
-          <t>2023-11-28</t>
+          <t>2023-11-29</t>
         </is>
       </c>
       <c r="F1852" t="inlineStr">
@@ -99992,7 +99992,7 @@
       </c>
       <c r="G1852" t="inlineStr">
         <is>
-          <t>ANOPHELES GALVAOI</t>
+          <t>ANOPHELES ALBITARSIS</t>
         </is>
       </c>
       <c r="H1852">
@@ -100005,12 +100005,12 @@
       </c>
       <c r="L1852" t="inlineStr">
         <is>
-          <t>-25.343179</t>
+          <t>-27.344119</t>
         </is>
       </c>
       <c r="M1852" t="inlineStr">
         <is>
-          <t>-57.645754</t>
+          <t>-57.651217</t>
         </is>
       </c>
     </row>
@@ -100035,7 +100035,7 @@
       </c>
       <c r="E1853" t="inlineStr">
         <is>
-          <t>2023-11-29</t>
+          <t>2023-11-30</t>
         </is>
       </c>
       <c r="F1853" t="inlineStr">
@@ -100058,12 +100058,12 @@
       </c>
       <c r="L1853" t="inlineStr">
         <is>
-          <t>-27.344119</t>
+          <t>-27.335509</t>
         </is>
       </c>
       <c r="M1853" t="inlineStr">
         <is>
-          <t>-57.651217</t>
+          <t>-57.63658</t>
         </is>
       </c>
     </row>
@@ -100247,7 +100247,7 @@
       </c>
       <c r="E1857" t="inlineStr">
         <is>
-          <t>2023-11-30</t>
+          <t>2023-11-28</t>
         </is>
       </c>
       <c r="F1857" t="inlineStr">
@@ -100270,12 +100270,12 @@
       </c>
       <c r="L1857" t="inlineStr">
         <is>
-          <t>-27.335509</t>
+          <t>-25.343179</t>
         </is>
       </c>
       <c r="M1857" t="inlineStr">
         <is>
-          <t>-57.63658</t>
+          <t>-57.645754</t>
         </is>
       </c>
     </row>
@@ -100310,7 +100310,7 @@
       </c>
       <c r="G1858" t="inlineStr">
         <is>
-          <t>ANOPHELES ALBITARSIS</t>
+          <t>ANOPHELES SPP</t>
         </is>
       </c>
       <c r="H1858">
@@ -100335,17 +100335,17 @@
     <row r="1859">
       <c r="A1859" t="inlineStr">
         <is>
-          <t>NEEMBUCU</t>
+          <t>SAN PEDRO</t>
         </is>
       </c>
       <c r="B1859" t="inlineStr">
         <is>
-          <t>CERRITO</t>
+          <t>ANTEQUERA</t>
         </is>
       </c>
       <c r="C1859" t="inlineStr">
         <is>
-          <t>CERRITO</t>
+          <t>ANTEQUERA</t>
         </is>
       </c>
       <c r="D1859">
@@ -100353,7 +100353,7 @@
       </c>
       <c r="E1859" t="inlineStr">
         <is>
-          <t>2023-11-28</t>
+          <t>2023-12-18</t>
         </is>
       </c>
       <c r="F1859" t="inlineStr">
@@ -100363,7 +100363,7 @@
       </c>
       <c r="G1859" t="inlineStr">
         <is>
-          <t>ANOPHELES SPP</t>
+          <t>ANOPHELES ALBITARSIS</t>
         </is>
       </c>
       <c r="H1859">
@@ -100376,12 +100376,12 @@
       </c>
       <c r="L1859" t="inlineStr">
         <is>
-          <t>-25.343179</t>
+          <t>-24.087057</t>
         </is>
       </c>
       <c r="M1859" t="inlineStr">
         <is>
-          <t>-57.645754</t>
+          <t>-57.19029</t>
         </is>
       </c>
     </row>
@@ -100406,7 +100406,7 @@
       </c>
       <c r="E1860" t="inlineStr">
         <is>
-          <t>2023-12-18</t>
+          <t>2023-12-19</t>
         </is>
       </c>
       <c r="F1860" t="inlineStr">
@@ -100429,12 +100429,12 @@
       </c>
       <c r="L1860" t="inlineStr">
         <is>
-          <t>-24.087057</t>
+          <t>-24.086525</t>
         </is>
       </c>
       <c r="M1860" t="inlineStr">
         <is>
-          <t>-57.19029</t>
+          <t>-57.176366</t>
         </is>
       </c>
     </row>
@@ -100469,7 +100469,7 @@
       </c>
       <c r="G1861" t="inlineStr">
         <is>
-          <t>ANOPHELES ALBITARSIS</t>
+          <t>ANOPHELES RONDONI</t>
         </is>
       </c>
       <c r="H1861">
@@ -100512,7 +100512,7 @@
       </c>
       <c r="E1862" t="inlineStr">
         <is>
-          <t>2023-12-19</t>
+          <t>2023-12-20</t>
         </is>
       </c>
       <c r="F1862" t="inlineStr">
@@ -100522,7 +100522,7 @@
       </c>
       <c r="G1862" t="inlineStr">
         <is>
-          <t>ANOPHELES RONDONI</t>
+          <t>ANOPHELES ALBITARSIS</t>
         </is>
       </c>
       <c r="H1862">
@@ -100535,12 +100535,12 @@
       </c>
       <c r="L1862" t="inlineStr">
         <is>
-          <t>-24.086525</t>
+          <t>-24.076316</t>
         </is>
       </c>
       <c r="M1862" t="inlineStr">
         <is>
-          <t>-57.176366</t>
+          <t>-57.207348</t>
         </is>
       </c>
     </row>
@@ -100565,7 +100565,7 @@
       </c>
       <c r="E1863" t="inlineStr">
         <is>
-          <t>2023-12-20</t>
+          <t>2023-12-19</t>
         </is>
       </c>
       <c r="F1863" t="inlineStr">
@@ -100575,7 +100575,7 @@
       </c>
       <c r="G1863" t="inlineStr">
         <is>
-          <t>ANOPHELES ALBITARSIS</t>
+          <t>ANOPHELES EVANSAE</t>
         </is>
       </c>
       <c r="H1863">
@@ -100588,12 +100588,12 @@
       </c>
       <c r="L1863" t="inlineStr">
         <is>
-          <t>-24.076316</t>
+          <t>-24.087057</t>
         </is>
       </c>
       <c r="M1863" t="inlineStr">
         <is>
-          <t>-57.207348</t>
+          <t>-57.19029</t>
         </is>
       </c>
     </row>
@@ -100628,7 +100628,7 @@
       </c>
       <c r="G1864" t="inlineStr">
         <is>
-          <t>ANOPHELES EVANSAE</t>
+          <t>ANOPHELES RONDONI</t>
         </is>
       </c>
       <c r="H1864">
@@ -100653,17 +100653,17 @@
     <row r="1865">
       <c r="A1865" t="inlineStr">
         <is>
-          <t>SAN PEDRO</t>
+          <t>BOQUERON</t>
         </is>
       </c>
       <c r="B1865" t="inlineStr">
         <is>
-          <t>ANTEQUERA</t>
+          <t>MARISCAL JOSE FELIX ESTIGARRIBIA</t>
         </is>
       </c>
       <c r="C1865" t="inlineStr">
         <is>
-          <t>ANTEQUERA</t>
+          <t>CUARTEL 6TA DIVISION</t>
         </is>
       </c>
       <c r="D1865">
@@ -100671,7 +100671,7 @@
       </c>
       <c r="E1865" t="inlineStr">
         <is>
-          <t>2023-12-19</t>
+          <t>2023-05-12</t>
         </is>
       </c>
       <c r="F1865" t="inlineStr">
@@ -100681,7 +100681,7 @@
       </c>
       <c r="G1865" t="inlineStr">
         <is>
-          <t>ANOPHELES RONDONI</t>
+          <t>ANOPHELES ALBITARSIS</t>
         </is>
       </c>
       <c r="H1865">
@@ -100694,12 +100694,12 @@
       </c>
       <c r="L1865" t="inlineStr">
         <is>
-          <t>-24.087057</t>
+          <t>-22.016963</t>
         </is>
       </c>
       <c r="M1865" t="inlineStr">
         <is>
-          <t>-57.19029</t>
+          <t>-60.61638</t>
         </is>
       </c>
     </row>
@@ -100716,7 +100716,7 @@
       </c>
       <c r="C1866" t="inlineStr">
         <is>
-          <t>CUARTEL 6TA DIVISION</t>
+          <t>29 DE SETIEMBRE: EXTRADOMICILIO</t>
         </is>
       </c>
       <c r="D1866">
@@ -100747,12 +100747,17 @@
       </c>
       <c r="L1866" t="inlineStr">
         <is>
-          <t>-22.016963</t>
+          <t>-21.441701527</t>
         </is>
       </c>
       <c r="M1866" t="inlineStr">
         <is>
-          <t>-60.61638</t>
+          <t>-61.470380659</t>
+        </is>
+      </c>
+      <c r="N1866" t="inlineStr">
+        <is>
+          <t>CENTROIDE DISTRITO</t>
         </is>
       </c>
     </row>
@@ -100787,7 +100792,7 @@
       </c>
       <c r="G1867" t="inlineStr">
         <is>
-          <t>ANOPHELES ALBITARSIS</t>
+          <t>ANOPHELES OSWALDOI</t>
         </is>
       </c>
       <c r="H1867">
@@ -100827,7 +100832,7 @@
       </c>
       <c r="C1868" t="inlineStr">
         <is>
-          <t>29 DE SETIEMBRE: EXTRADOMICILIO</t>
+          <t>29 DE SETIEMBRE</t>
         </is>
       </c>
       <c r="D1868">
@@ -100845,7 +100850,7 @@
       </c>
       <c r="G1868" t="inlineStr">
         <is>
-          <t>ANOPHELES OSWALDOI</t>
+          <t>ANOPHELES ALBITARSIS</t>
         </is>
       </c>
       <c r="H1868">
@@ -100885,7 +100890,7 @@
       </c>
       <c r="C1869" t="inlineStr">
         <is>
-          <t>29 DE SETIEMBRE</t>
+          <t>AL LADO DEL HOSPITAL DISTRITAL</t>
         </is>
       </c>
       <c r="D1869">
@@ -100916,17 +100921,12 @@
       </c>
       <c r="L1869" t="inlineStr">
         <is>
-          <t>-21.441701527</t>
+          <t>-22.020357</t>
         </is>
       </c>
       <c r="M1869" t="inlineStr">
         <is>
-          <t>-61.470380659</t>
-        </is>
-      </c>
-      <c r="N1869" t="inlineStr">
-        <is>
-          <t>CENTROIDE DISTRITO</t>
+          <t>-60.599674</t>
         </is>
       </c>
     </row>
@@ -100943,7 +100943,7 @@
       </c>
       <c r="C1870" t="inlineStr">
         <is>
-          <t>AL LADO DEL HOSPITAL DISTRITAL</t>
+          <t>29 DE SETIEMBRE, CASA PACIENTE</t>
         </is>
       </c>
       <c r="D1870">
@@ -100961,7 +100961,7 @@
       </c>
       <c r="G1870" t="inlineStr">
         <is>
-          <t>ANOPHELES ALBITARSIS</t>
+          <t>ANOPHELES OSWALDOI</t>
         </is>
       </c>
       <c r="H1870">
@@ -100974,12 +100974,17 @@
       </c>
       <c r="L1870" t="inlineStr">
         <is>
-          <t>-22.020357</t>
+          <t>-21.441701527</t>
         </is>
       </c>
       <c r="M1870" t="inlineStr">
         <is>
-          <t>-60.599674</t>
+          <t>-61.470380659</t>
+        </is>
+      </c>
+      <c r="N1870" t="inlineStr">
+        <is>
+          <t>CENTROIDE DISTRITO</t>
         </is>
       </c>
     </row>
@@ -100996,7 +101001,7 @@
       </c>
       <c r="C1871" t="inlineStr">
         <is>
-          <t>29 DE SETIEMBRE, CASA PACIENTE</t>
+          <t>HOSPITAL DISTRITAL</t>
         </is>
       </c>
       <c r="D1871">
@@ -101014,7 +101019,7 @@
       </c>
       <c r="G1871" t="inlineStr">
         <is>
-          <t>ANOPHELES OSWALDOI</t>
+          <t>ANOPHELES EVANSAE</t>
         </is>
       </c>
       <c r="H1871">
@@ -101027,17 +101032,12 @@
       </c>
       <c r="L1871" t="inlineStr">
         <is>
-          <t>-21.441701527</t>
+          <t>-22.019886</t>
         </is>
       </c>
       <c r="M1871" t="inlineStr">
         <is>
-          <t>-61.470380659</t>
-        </is>
-      </c>
-      <c r="N1871" t="inlineStr">
-        <is>
-          <t>CENTROIDE DISTRITO</t>
+          <t>-60.599939</t>
         </is>
       </c>
     </row>
@@ -101072,7 +101072,7 @@
       </c>
       <c r="G1872" t="inlineStr">
         <is>
-          <t>ANOPHELES EVANSAE</t>
+          <t>ANOPHELES OSWALDOI</t>
         </is>
       </c>
       <c r="H1872">
@@ -101089,59 +101089,6 @@
         </is>
       </c>
       <c r="M1872" t="inlineStr">
-        <is>
-          <t>-60.599939</t>
-        </is>
-      </c>
-    </row>
-    <row r="1873">
-      <c r="A1873" t="inlineStr">
-        <is>
-          <t>BOQUERON</t>
-        </is>
-      </c>
-      <c r="B1873" t="inlineStr">
-        <is>
-          <t>MARISCAL JOSE FELIX ESTIGARRIBIA</t>
-        </is>
-      </c>
-      <c r="C1873" t="inlineStr">
-        <is>
-          <t>HOSPITAL DISTRITAL</t>
-        </is>
-      </c>
-      <c r="D1873">
-        <v>2023</v>
-      </c>
-      <c r="E1873" t="inlineStr">
-        <is>
-          <t>2023-05-12</t>
-        </is>
-      </c>
-      <c r="F1873" t="inlineStr">
-        <is>
-          <t>MALARIA</t>
-        </is>
-      </c>
-      <c r="G1873" t="inlineStr">
-        <is>
-          <t>ANOPHELES OSWALDOI</t>
-        </is>
-      </c>
-      <c r="H1873">
-        <v>21</v>
-      </c>
-      <c r="I1873" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="L1873" t="inlineStr">
-        <is>
-          <t>-22.019886</t>
-        </is>
-      </c>
-      <c r="M1873" t="inlineStr">
         <is>
           <t>-60.599939</t>
         </is>
